--- a/runs/RELX/2026-10-14/bear/scratch/gs_strict_peer_g7/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_strict_peer_g7/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2353.816018034002</v>
+        <v>2405.6123185187</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.09208</v>
+        <v>0.08606720000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.08636291564</v>
+        <v>0.08112083634400001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>12081.17632718196</v>
+        <v>12227.16039301127</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>52234.18625270405</v>
+        <v>56969.77576700412</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>35980.53687531454</v>
+        <v>40106.10081028486</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>48061.7132024965</v>
+        <v>52333.26120329613</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>41064.7132024965</v>
+        <v>45336.26120329613</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>40725.86561958607</v>
+        <v>45092.95641241787</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>23.35527181030321</v>
+        <v>25.85968984869618</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2335.527181030321</v>
+        <v>2585.968984869618</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.1571536698</v>
+        <v>-0.06677409419999999</v>
       </c>
     </row>
   </sheetData>
